--- a/tabelas_classes_excel/Tabela_3-9_O_Feiticeiro.xlsx
+++ b/tabelas_classes_excel/Tabela_3-9_O_Feiticeiro.xlsx
@@ -757,18 +757,12 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>INFORMAÇÕES DE</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -956,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1009,31 +1003,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1045,73 +1014,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base</t>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>de Ataque</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fortitude</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Reflexos</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vontade Especial</t>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Invocar familiar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>2°</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>+0</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>+0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Invocar familiar</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1121,51 +1120,61 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>+3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>4°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,40 +1195,50 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>+4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1240,18 +1259,23 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1266,14 +1290,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1283,29 +1312,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>+6</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1320,14 +1354,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1348,40 +1387,50 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>+7</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1402,18 +1451,23 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>+8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1428,14 +1482,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1445,29 +1504,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>+9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1482,14 +1546,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1510,40 +1579,50 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>+10</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1564,18 +1643,23 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>+11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1590,524 +1674,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+11</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+10/+5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>+12</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Outras Classes: Os feiticeiros consideram que têm mais em comum com os</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prejudicam os gestos arcanos de u</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>membros de outras classes autodidatas, como os druidas e os ladinos. Muitas</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>tenham componentes gestuais fraca</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>vezes, eles entram em conflito com os membros de classes mais disciplina-</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Magias: Um feiticeiro conjur</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>das, como os paladinos e os monges. Como podem conjurar as mesmas</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>disponíveis p</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>magias que os magos, embora de modo diferente, algumas vezes essas</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>classes competem entre si.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Função: A função de um feiticeiro é definida com base</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>em sua seleção de magias. Um feiticeiro que se concentre</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Hennet</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>em magias de combate se tornará o centro ofensivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>do grupo. Outros podem escolher magias mais sutis,</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>como encantamentos e ilusões, e assumir uma função</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>secundária. Um grupo que tenha um feiticeiro deve</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>considerar a hipótese de incluir um segundo conju-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>rador, como um bardo, um clérigo, um druida ou</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>mesmo um mago, devido a falta de versatilidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>do feiticeiro. Como têm uma presença marcante,</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>somen</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>que lhes permite impressionar as pessoas, muitas</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>magias d</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>vezes os feiticeiros atuam como porta-vozes de um</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>encontra n</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>grupo de aventureiros, negociando, barganhando e</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>feitic</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>conversando em nome do grupo. As magias do fei-</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>(con</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ticeiro o auxiliam a influenciar as pessoas ou obter</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>informações, tornando-o um excelente espião ou</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>diplomata para um grupo de aventureiros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>INFORMAÇÕES DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>JOGO</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Os feiticeiros possuem as seguintes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>estatísticas de jogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Habilidades: O Carisma determina</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>a magia mais poderosa que um feiticeiro</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>é capaz de conjurar, a quantidade de magias disponíveis a cada dia e</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>a dificuldade para resistir às suas magias (consulte Magias, a seguir).</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Semelhante aos magos, um feiticeiro se beneficia de valores elevados</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>de Destreza e Constituição.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>e pesquis</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Tendência: Qualquer uma.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>ou grimó</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Dado de Vida: d4.</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>não exi</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>poderia s</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Perícias de Classe</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>adquirir um n</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um feiticeiro (e a habilidade chave para cada perícia)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>personagem. De qualquer forma, el</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>são: Blefar (Car), Concentração (Con), Conhecimento (arcano) (Int), Identificar</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>magias mais rapidamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Magia (Int), Ofícios (Int) e Profissão (Sab). Consulte o Capítulo 4: Perícias para</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Quando alcançar o 4° nível,</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>obter as descrições das perícias.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>12°, 14°, 16°, 18° e 20°), um fei</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia no 1° nível: (2 + modificador de Int) x4.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>substituição a um efeito antigo d</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia a cada nível subseqüente: 2 + modificador de Inteligên-</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>magia antiga e aprende a nova. O</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cia.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>idêntico; o feiticeiro somente co</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>ao seu nível máximo disponível. P</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Características da Classe</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>substituir uma magia de nível 0 (</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Usar Armas e Armaduras: O feiticeiro sabe usar todas as armas simples. Ele</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>disponível ao feiticeiro, que são</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>não sabe usar nenhum tipo de armadura ou escudos. As armaduras de qualquer tipo</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>No 6° nível, ele poderia trocar u</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>acesso a magias de feiticeiro de</t>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
